--- a/artfynd/A 10475-2026 artfynd.xlsx
+++ b/artfynd/A 10475-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132221108</v>
+        <v>132246451</v>
       </c>
       <c r="B2" t="n">
-        <v>79277</v>
+        <v>57914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723249</v>
+        <v>723112</v>
       </c>
       <c r="R2" t="n">
-        <v>7097705</v>
+        <v>7097800</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,63 +756,71 @@
           <t>2026-03-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I närheten av bohål som kan vara gjort av tretåig hackspett men bohålet är en osäker artbestämning</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132221703</v>
+        <v>132246606</v>
       </c>
       <c r="B3" t="n">
-        <v>57914</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723111</v>
+        <v>723276</v>
       </c>
       <c r="R3" t="n">
-        <v>7097799</v>
+        <v>7097755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,71 +866,62 @@
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack se bild</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132166557</v>
+        <v>132246941</v>
       </c>
       <c r="B4" t="n">
-        <v>99054</v>
+        <v>79276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723275</v>
+        <v>723249</v>
       </c>
       <c r="R4" t="n">
-        <v>7097754</v>
+        <v>7097705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +967,6 @@
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>20st</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -981,22 +980,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132221082</v>
+        <v>132246786</v>
       </c>
       <c r="B5" t="n">
-        <v>79277</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,16 +1003,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1034,7 +1033,7 @@
         <v>723234</v>
       </c>
       <c r="R5" t="n">
-        <v>7097810</v>
+        <v>7097811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,15 +1081,116 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132221082</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79277</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långåker, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>723234</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7097810</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Max Brändström Nyström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Max Brändström Nyström, Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10475-2026 artfynd.xlsx
+++ b/artfynd/A 10475-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246451</v>
       </c>
       <c r="B2" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132246606</v>
       </c>
       <c r="B3" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>132246941</v>
       </c>
       <c r="B4" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>132246786</v>
       </c>
       <c r="B5" t="n">
-        <v>79276</v>
+        <v>79310</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>132221082</v>
       </c>
       <c r="B6" t="n">
-        <v>79277</v>
+        <v>79311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10475-2026 artfynd.xlsx
+++ b/artfynd/A 10475-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132246606</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132246941</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>132246786</v>
       </c>
       <c r="B4" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>132221082</v>
       </c>
       <c r="B5" t="n">
-        <v>79316</v>
+        <v>79318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 10475-2026 artfynd.xlsx
+++ b/artfynd/A 10475-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132246606</v>
+        <v>132246786</v>
       </c>
       <c r="B2" t="n">
-        <v>99122</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723276</v>
+        <v>723234</v>
       </c>
       <c r="R2" t="n">
-        <v>7097755</v>
+        <v>7097811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,11 +779,11 @@
         <v>132246941</v>
       </c>
       <c r="B3" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -882,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132246786</v>
+        <v>132246451</v>
       </c>
       <c r="B4" t="n">
-        <v>79329</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,26 +888,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723234</v>
+        <v>723081</v>
       </c>
       <c r="R4" t="n">
-        <v>7097811</v>
+        <v>7097764</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,13 +958,17 @@
           <t>2026-03-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I närheten av bohål som kan vara gjort av tretåig hackspett men bohålet är en osäker artbestämning</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,37 +987,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132221082</v>
+        <v>132246606</v>
       </c>
       <c r="B5" t="n">
-        <v>79330</v>
+        <v>99195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723234</v>
+        <v>723276</v>
       </c>
       <c r="R5" t="n">
-        <v>7097810</v>
+        <v>7097755</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1081,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Max Brändström Nyström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1084,42 +1093,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132246451</v>
+        <v>132221082</v>
       </c>
       <c r="B6" t="n">
-        <v>57957</v>
+        <v>79374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1127,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723081</v>
+        <v>723234</v>
       </c>
       <c r="R6" t="n">
-        <v>7097764</v>
+        <v>7097810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,24 +1169,20 @@
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I närheten av bohål som kan vara gjort av tretåig hackspett men bohålet är en osäker artbestämning</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Max Brändström Nyström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">

--- a/artfynd/A 10475-2026 artfynd.xlsx
+++ b/artfynd/A 10475-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132246786</v>
+        <v>132246941</v>
       </c>
       <c r="B2" t="n">
         <v>79373</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723234</v>
+        <v>723249</v>
       </c>
       <c r="R2" t="n">
-        <v>7097811</v>
+        <v>7097705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -773,424 +773,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>132246941</v>
-      </c>
-      <c r="B3" t="n">
-        <v>79373</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Långåker, Vb</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>723249</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7097705</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Vännäs</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Vännäs</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>132246451</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Långåker, Vb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>723081</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7097764</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Vännäs</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Vännäs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I närheten av bohål som kan vara gjort av tretåig hackspett men bohålet är en osäker artbestämning</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>132246606</v>
-      </c>
-      <c r="B5" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Långåker, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>723276</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7097755</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Vännäs</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Vännäs</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>132221082</v>
-      </c>
-      <c r="B6" t="n">
-        <v>79374</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Långåker, Vb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>723234</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7097810</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Vännäs</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Vännäs</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Max Brändström Nyström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10475-2026 artfynd.xlsx
+++ b/artfynd/A 10475-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,8 +778,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132246941</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>